--- a/artfynd/A 17970-2022 artfynd.xlsx
+++ b/artfynd/A 17970-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 17970-2022 artfynd.xlsx
+++ b/artfynd/A 17970-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>108120750</v>
+        <v>108120422</v>
       </c>
       <c r="B2" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,13 +708,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,13 +721,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>518839.9999533196</v>
+        <v>518815</v>
       </c>
       <c r="R2" t="n">
-        <v>6549245.441131983</v>
+        <v>6549300</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -781,6 +775,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -799,46 +794,44 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>108120553</v>
+        <v>108120750</v>
       </c>
       <c r="B3" t="n">
-        <v>5426</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>101410</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -848,13 +841,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518829.4952565805</v>
+        <v>518840</v>
       </c>
       <c r="R3" t="n">
-        <v>6549287.534511666</v>
+        <v>6549245</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -902,7 +895,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -921,51 +913,43 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>108120611</v>
+        <v>108120553</v>
       </c>
       <c r="B4" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5495</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>101410</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -973,13 +957,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518839.9999533196</v>
+        <v>518829</v>
       </c>
       <c r="R4" t="n">
-        <v>6549245.441131983</v>
+        <v>6549288</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1043,6 +1027,243 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>108120396</v>
+      </c>
+      <c r="B5" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Källbergsbacksbergen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>518789</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6549286</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Sköllersta</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-04-14</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-04-14</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>108120611</v>
+      </c>
+      <c r="B6" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Källbergsbacksbergen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>518840</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6549245</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Sköllersta</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-04-14</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-04-14</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 17970-2022 artfynd.xlsx
+++ b/artfynd/A 17970-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108120422</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -910,6 +920,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108120750</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1027,6 +1042,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108120553</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1144,6 +1164,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108120396</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1264,8 +1289,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108120611</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>